--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92573722803</v>
+        <v>46157.93114976384</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93114976384</v>
+        <v>46157.9318154203</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9318154203</v>
+        <v>46157.93405066125</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405066125</v>
+        <v>46157.93723131608</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723131608</v>
+        <v>46158.28220972322</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28220972322</v>
+        <v>46158.29698474935</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29698474935</v>
+        <v>46158.29820642707</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29820642707</v>
+        <v>46158.33391981854</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33391981854</v>
+        <v>46158.36861773138</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Исламова- делопроизводитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36861773138</v>
+        <v>46158.37292418044</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
